--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_25_inference.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_25_inference.xlsx
@@ -31,58 +31,58 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>vm_tot</t>
+  </si>
+  <si>
     <t>nn_input</t>
   </si>
   <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>qinj_tot</t>
+    <t>pd_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
   </si>
   <si>
     <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>vm_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>pd_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
   </si>
   <si>
     <t>25533.27 (26155.34 &gt; 2.33%)</t>
@@ -489,16 +489,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>7.800246544737776E-17</v>
+        <v>0.4184427857398987</v>
       </c>
       <c r="C2">
-        <v>7.800246544737776E-17</v>
+        <v>0.4184427857398987</v>
       </c>
       <c r="D2">
-        <v>7.800246544737776E-17</v>
+        <v>0.03039162047207355</v>
       </c>
       <c r="E2">
-        <v>7.800246544737776E-17</v>
+        <v>0.07307588309049606</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -506,16 +506,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0.02462570351491198</v>
+        <v>0.01286289375275373</v>
       </c>
       <c r="C3">
-        <v>0.02462419948679093</v>
+        <v>0.01286537852138281</v>
       </c>
       <c r="D3">
-        <v>0.004633716307580471</v>
+        <v>6.402133294614032E-05</v>
       </c>
       <c r="E3">
-        <v>0.01734122633934021</v>
+        <v>0.0001545327831991017</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -523,16 +523,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.06321419030427933</v>
+        <v>0.002635866105276887</v>
       </c>
       <c r="C4">
-        <v>0.06321495026350021</v>
+        <v>0.004482212105449183</v>
       </c>
       <c r="D4">
-        <v>0.00433445256203413</v>
+        <v>0.1682066470384598</v>
       </c>
       <c r="E4">
-        <v>0.01878824271261692</v>
+        <v>0.4750751256942749</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -540,16 +540,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0.1295129805803299</v>
+        <v>0.1207198581330253</v>
       </c>
       <c r="C5">
-        <v>0.1295180320739746</v>
+        <v>0.1207246758028618</v>
       </c>
       <c r="D5">
-        <v>0.08685509115457535</v>
+        <v>0.08672726154327393</v>
       </c>
       <c r="E5">
-        <v>0.05466794222593307</v>
+        <v>0.05430397018790245</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -557,33 +557,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.006891468137640602</v>
+        <v>0.006807375369346996</v>
       </c>
       <c r="C6">
-        <v>0.006891364810731529</v>
+        <v>0.006807263375233425</v>
       </c>
       <c r="D6">
-        <v>0.001502991421148181</v>
+        <v>0.001455917023122311</v>
       </c>
       <c r="E6">
-        <v>0.003969941753894091</v>
+        <v>0.003960506524890661</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7">
-        <v>0.0006704461993649602</v>
-      </c>
-      <c r="C7">
-        <v>0.0006704439292661846</v>
-      </c>
-      <c r="D7">
-        <v>4.093202005606145E-05</v>
-      </c>
-      <c r="E7">
-        <v>0.0001061286966432817</v>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -591,33 +591,33 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.01286289375275373</v>
+        <v>0.05882032004524018</v>
       </c>
       <c r="C8">
-        <v>0.01286537852138281</v>
+        <v>0.05882878904107128</v>
       </c>
       <c r="D8">
-        <v>6.402133294614032E-05</v>
+        <v>0.0182314608246088</v>
       </c>
       <c r="E8">
-        <v>0.0001545327831991017</v>
+        <v>0.01460416615009308</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>29</v>
+      <c r="B9">
+        <v>0.06321419030427933</v>
+      </c>
+      <c r="C9">
+        <v>0.06321495026350021</v>
+      </c>
+      <c r="D9">
+        <v>0.004334451630711555</v>
+      </c>
+      <c r="E9">
+        <v>0.01878824830055237</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -625,33 +625,33 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.05882032006985059</v>
+        <v>0.05886798206949161</v>
       </c>
       <c r="C10">
-        <v>0.05882878904050766</v>
+        <v>0.05887644439863806</v>
       </c>
       <c r="D10">
-        <v>0.0182314608246088</v>
+        <v>0.01810950227081776</v>
       </c>
       <c r="E10">
-        <v>0.01460416615009308</v>
+        <v>0.01462099887430668</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -659,16 +659,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>0.0006704461993649602</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.0006704439292661846</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>4.093202005606145E-05</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>0.0001061286966432817</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -676,16 +676,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.001370642450638115</v>
+        <v>7.800246555488042E-17</v>
       </c>
       <c r="C13">
-        <v>0.001370779005810618</v>
+        <v>7.800246555488042E-17</v>
       </c>
       <c r="D13">
-        <v>4.212586281937547E-05</v>
+        <v>7.800246555488042E-17</v>
       </c>
       <c r="E13">
-        <v>0.0001118856598623097</v>
+        <v>7.800246555488042E-17</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -693,16 +693,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.05886798209409079</v>
+        <v>0.001370642450638115</v>
       </c>
       <c r="C14">
-        <v>0.05887644439807262</v>
+        <v>0.001370779005810618</v>
       </c>
       <c r="D14">
-        <v>0.01810950413346291</v>
+        <v>4.212586281937547E-05</v>
       </c>
       <c r="E14">
-        <v>0.01462099887430668</v>
+        <v>0.0001118856598623097</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -710,16 +710,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>0.006891468137234335</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>0.006891364810776591</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>0.001502991653978825</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>0.003969940822571516</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -727,16 +727,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.1207198581627726</v>
+        <v>0.02462570351671281</v>
       </c>
       <c r="C16">
-        <v>0.1207246758009666</v>
+        <v>0.02462419948692706</v>
       </c>
       <c r="D16">
-        <v>0.08672726154327393</v>
+        <v>0.004633715376257896</v>
       </c>
       <c r="E16">
-        <v>0.05430397018790245</v>
+        <v>0.01734123006463051</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -744,33 +744,33 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.002635866586004651</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>0.004482211961263738</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0.1682066321372986</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0.4750751852989197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18">
-        <v>0.4184427857398987</v>
-      </c>
-      <c r="C18">
-        <v>0.4184427857398987</v>
-      </c>
-      <c r="D18">
-        <v>0.030391626060009</v>
-      </c>
-      <c r="E18">
-        <v>0.07307583838701248</v>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -778,16 +778,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.006807375369737106</v>
+        <v>0.1295129805803299</v>
       </c>
       <c r="C19">
-        <v>0.00680726337518855</v>
+        <v>0.1295180320739746</v>
       </c>
       <c r="D19">
-        <v>0.001455916790291667</v>
+        <v>0.08685508370399475</v>
       </c>
       <c r="E19">
-        <v>0.003960506524890661</v>
+        <v>0.05466794222593307</v>
       </c>
     </row>
   </sheetData>
